--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1709-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1709-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E8EE5C4-9072-4EE0-9D6B-9C7BAF65FF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31D7E0CE-26CB-4CEC-A17B-1535FD5D15FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CEE8A3B3-4AD6-41E3-9F80-D756104DC10E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A8C434E5-6C6A-49F2-91B7-97AF2C454678}"/>
   </bookViews>
   <sheets>
     <sheet name="1709-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1577,28 +1577,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB431871-27F0-4410-9522-9FBC8C8469ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C007D8E3-90C1-4D94-94D7-6F6BE4802DBC}">
   <dimension ref="A1:X56"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1668,7 +1668,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1788,7 +1788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2023</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>2022</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2021</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <v>2020</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2019</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>2018</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2017</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>2016</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2015</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2014</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2013</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>2012</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2011</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2010</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2009</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2008</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2007</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2006</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2005</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>2004</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>2003</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>2002</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2001</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="42">
         <v>2000</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="44"/>
       <c r="B38" s="45"/>
       <c r="C38" s="21" t="s">
@@ -4206,7 +4206,7 @@
       <c r="W38" s="51"/>
       <c r="X38" s="47"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1999</v>
       </c>
@@ -4278,7 +4278,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>1998</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1997</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <v>1996</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1995</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
         <v>1994</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1993</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1992</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1991</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1990</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1989</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>1988</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1987</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
         <v>1986</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>1985</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="40">
         <v>1984</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>1983</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="40" t="s">
         <v>67</v>
       </c>
